--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.99357310135751</v>
+        <v>7.148955628970595</v>
       </c>
       <c r="D2" t="n">
-        <v>44.00135758275</v>
+        <v>7.150220607196876</v>
       </c>
       <c r="E2" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F2" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.1788123464293</v>
+        <v>4.904057006294762</v>
       </c>
       <c r="D3" t="n">
-        <v>29.90135522352773</v>
+        <v>4.858970223823256</v>
       </c>
       <c r="E3" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F3" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.21668774699496</v>
+        <v>5.722711758886681</v>
       </c>
       <c r="D4" t="n">
-        <v>35.19280747501563</v>
+        <v>5.718831214690041</v>
       </c>
       <c r="E4" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F4" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.77102023580052</v>
+        <v>2.562790788317584</v>
       </c>
       <c r="D5" t="n">
-        <v>15.79258730145298</v>
+        <v>2.566295436486109</v>
       </c>
       <c r="E5" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F5" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.00151882565699</v>
+        <v>3.900246809169261</v>
       </c>
       <c r="D6" t="n">
-        <v>23.9780933776828</v>
+        <v>3.896440173873456</v>
       </c>
       <c r="E6" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F6" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.78047378612413</v>
+        <v>3.376826990245171</v>
       </c>
       <c r="D7" t="n">
-        <v>21.37698482589247</v>
+        <v>3.473760034207527</v>
       </c>
       <c r="E7" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F7" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.80913984903388</v>
+        <v>5.818985225468007</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79061325826915</v>
+        <v>5.815974654468738</v>
       </c>
       <c r="E8" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F8" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.4224875409957</v>
+        <v>5.756154225411802</v>
       </c>
       <c r="D9" t="n">
-        <v>35.90565038648377</v>
+        <v>5.834668187803613</v>
       </c>
       <c r="E9" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F9" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.57689244473702</v>
+        <v>6.106245022269766</v>
       </c>
       <c r="D10" t="n">
-        <v>37.59169784254775</v>
+        <v>6.10865089941401</v>
       </c>
       <c r="E10" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F10" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.8999741241945</v>
+        <v>7.133745795181606</v>
       </c>
       <c r="D11" t="n">
-        <v>43.89708237491868</v>
+        <v>7.133275885924286</v>
       </c>
       <c r="E11" t="n">
-        <v>8.99430029205077</v>
+        <v>1.46157379745825</v>
       </c>
       <c r="F11" t="n">
-        <v>8.942962644938905</v>
+        <v>1.453231429802572</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
